--- a/Issues.xlsx
+++ b/Issues.xlsx
@@ -8,14 +8,14 @@
     <sheet name="Other" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Other'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Other'!$A$1:$C$17</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Catagory</t>
   </si>
@@ -75,15 +75,6 @@
   </si>
   <si>
     <t>Update-PSConfigFileCredentials</t>
-  </si>
-  <si>
-    <t>Not Copied</t>
-  </si>
-  <si>
-    <t>Show-PSConfigFile</t>
-  </si>
-  <si>
-    <t>&lt;=</t>
   </si>
 </sst>
 </file>
@@ -135,7 +126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.148280143737793" customWidth="1"/>
@@ -319,19 +310,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C18"/>
+  <autoFilter ref="A1:C17"/>
   <headerFooter/>
 </worksheet>
 </file>